--- a/deliverables/vendor_sql_issue_summary.xlsx
+++ b/deliverables/vendor_sql_issue_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bic-pannawat/Documents/SideProject/deliverables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F613F3-B333-3E42-91F2-A5C142DAEACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EA902D-EEB1-F343-95BF-69AC4B8DC3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="34400" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -650,9 +650,9 @@
   <cols>
     <col min="1" max="1" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="255.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="124" style="1" customWidth="1"/>
     <col min="6" max="6" width="36.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -845,9 +845,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -870,7 +870,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -893,7 +893,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -916,7 +916,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -939,7 +939,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -962,7 +962,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -985,7 +985,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1154,9 +1154,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>62</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>74</v>
       </c>
